--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486276_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486276_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1897</v>
+        <v>7.7553</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1423</v>
+        <v>5.7696</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0473</v>
+        <v>1.9857</v>
       </c>
       <c r="G2" t="n">
         <v>3.792</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0839</v>
+        <v>0.6495</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.399</v>
+        <v>0.2283</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4828</v>
+        <v>0.4212</v>
       </c>
       <c r="V2" t="n">
         <v>1.5737</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4269</v>
+        <v>6.5098</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1511</v>
+        <v>4.6175</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2759</v>
+        <v>1.8923</v>
       </c>
       <c r="G3" t="n">
         <v>4.1689</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3064</v>
+        <v>-0.2235</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7042</v>
+        <v>0.1707</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0106</v>
+        <v>-0.3942</v>
       </c>
       <c r="V3" t="n">
         <v>2.9995</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5351</v>
+        <v>2.3281</v>
       </c>
       <c r="E4" t="n">
-        <v>0.183</v>
+        <v>-0.5308</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3521</v>
+        <v>2.8589</v>
       </c>
       <c r="G4" t="n">
         <v>1.1442</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3822</v>
+        <v>1.1753</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1596</v>
+        <v>0.4458</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2226</v>
+        <v>0.7294</v>
       </c>
       <c r="V4" t="n">
         <v>0.4437</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2078</v>
+        <v>0.9856</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0016</v>
+        <v>0.142</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2062</v>
+        <v>0.8436</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9626</v>
+        <v>-0.1353</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3194</v>
+        <v>-0.9306</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.6432</v>
+        <v>0.7953</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1065</v>
+        <v>-0.477</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8609</v>
+        <v>-0.2492</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9674</v>
+        <v>-0.2279</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8561</v>
+        <v>0.3417</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1803</v>
+        <v>-0.6814</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6758</v>
+        <v>1.0231</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8276</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0451</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4641</v>
+        <v>0.2286</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7607</v>
+        <v>0.2716</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7034</v>
+        <v>-0.043</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1213</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6863</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9933999999999999</v>
+        <v>-0.1704</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3656</v>
+        <v>-0.5752</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6278</v>
+        <v>0.4048</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1353</v>
+        <v>-2.9626</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9306</v>
+        <v>-0.3194</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7953</v>
+        <v>-2.6432</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.477</v>
+        <v>-1.1065</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2492</v>
+        <v>0.8609</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2279</v>
+        <v>-1.9674</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3417</v>
+        <v>-1.8561</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6814</v>
+        <v>-1.1803</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0231</v>
+        <v>-0.6758</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>2.8276</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>3.0451</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2364</v>
+        <v>0.0859</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4951</v>
+        <v>0.1839</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2587</v>
+        <v>-0.098</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1952</v>
+        <v>-0.1213</v>
       </c>
       <c r="W6" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7602</v>
+        <v>-0.6863</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4176</v>
+        <v>-0.2327</v>
       </c>
       <c r="E7" t="n">
         <v>-0.8923</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4747</v>
+        <v>0.6596</v>
       </c>
       <c r="G7" t="n">
         <v>1.0158</v>
@@ -1000,13 +1000,13 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0668</v>
+        <v>0.2518</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1233</v>
+        <v>0.3082</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1705</v>
+        <v>-0.7618</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4656</v>
+        <v>-1.1678</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2951</v>
+        <v>0.406</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6466</v>
+        <v>0.1554</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4927</v>
+        <v>-0.9275</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1538</v>
+        <v>1.0829</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3971</v>
+        <v>1.7071</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0547</v>
+        <v>0.8823</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4519</v>
+        <v>0.8248</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2495</v>
+        <v>-1.5517</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5475</v>
+        <v>-1.8098</v>
       </c>
       <c r="O8" t="n">
-        <v>0.298</v>
+        <v>0.2582</v>
       </c>
       <c r="P8" t="n">
-        <v>0.435</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.4377</v>
       </c>
       <c r="R8" t="n">
-        <v>0.435</v>
+        <v>2.6101</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0411</v>
+        <v>-0.0331</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.3028</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1096</v>
+        <v>-0.3359</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.9434</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3165</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8451</v>
+        <v>-0.7735</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0543</v>
+        <v>-1.1303</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7907</v>
+        <v>0.3568</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5324</v>
+        <v>-1.6466</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0789</v>
+        <v>-0.4927</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4535</v>
+        <v>-1.1538</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3082</v>
+        <v>-1.3971</v>
       </c>
       <c r="K9" t="n">
-        <v>0.703</v>
+        <v>0.0547</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0112</v>
+        <v>-1.4519</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2241</v>
+        <v>-0.2495</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7819</v>
+        <v>-0.5475</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4423</v>
+        <v>0.298</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.8276</v>
+        <v>0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.7852</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.31</v>
+        <v>0.438</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.2668</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3942</v>
+        <v>0.1712</v>
       </c>
       <c r="V9" t="n">
-        <v>2.8249</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.9549</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9345</v>
+        <v>-1.7081</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1556</v>
+        <v>-0.9173</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2211</v>
+        <v>-0.7907</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1554</v>
+        <v>-1.5324</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9275</v>
+        <v>-0.0789</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0829</v>
+        <v>-1.4535</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7071</v>
+        <v>-0.3082</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8823</v>
+        <v>0.703</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8248</v>
+        <v>-1.0112</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5517</v>
+        <v>-1.2241</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8098</v>
+        <v>-0.7819</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2582</v>
+        <v>-0.4423</v>
       </c>
       <c r="P10" t="n">
         <v>-2.8276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.4377</v>
+        <v>-4.7852</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2058</v>
+        <v>-0.173</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.2211</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5208</v>
+        <v>-0.3942</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9434</v>
+        <v>2.8249</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2599</v>
+        <v>3.9549</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3165</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3375</v>
+        <v>-2.2565</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1309</v>
+        <v>-2.0192</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2065</v>
+        <v>-0.2374</v>
       </c>
       <c r="G11" t="n">
         <v>1.0269</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1131</v>
+        <v>-0.0321</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3749</v>
+        <v>-0.2632</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2618</v>
+        <v>0.231</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3812</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6804</v>
+        <v>-2.6811</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7373</v>
+        <v>-2.8612</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0569</v>
+        <v>0.1802</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2813</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0294</v>
+        <v>-0.03</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6165</v>
+        <v>0.2596</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4129</v>
+        <v>-0.2896</v>
       </c>
       <c r="V12" t="n">
         <v>0.1952</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9673</v>
+        <v>8.994700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5924000000000014</v>
+        <v>0.4350000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>8.559900000000001</v>
+        <v>8.559800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.745</v>
+        <v>1.744999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-2.4025</v>
@@ -1447,7 +1447,7 @@
         <v>7.3163</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8207999999999998</v>
+        <v>0.8207999999999993</v>
       </c>
       <c r="M13" t="n">
         <v>-6.392300000000001</v>
@@ -1468,13 +1468,13 @@
         <v>18.4882</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3098</v>
+        <v>2.3374</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0033</v>
+        <v>2.0309</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3063000000000001</v>
+        <v>0.3061</v>
       </c>
       <c r="V13" t="n">
         <v>7.0875</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2689</v>
+        <v>4.6594</v>
       </c>
       <c r="E14" t="n">
         <v>2.946</v>
       </c>
       <c r="F14" t="n">
-        <v>1.323</v>
+        <v>1.7134</v>
       </c>
       <c r="G14" t="n">
         <v>2.248</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3493</v>
+        <v>0.0412</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0408</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3085</v>
+        <v>0.082</v>
       </c>
       <c r="V14" t="n">
         <v>0.1952</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9503</v>
+        <v>3.1353</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5498</v>
+        <v>-0.9968</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5001</v>
+        <v>4.1321</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7758</v>
@@ -1624,13 +1624,13 @@
         <v>3.0451</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4009</v>
+        <v>0.5858</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.2007</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2468</v>
+        <v>0.3851</v>
       </c>
       <c r="V15" t="n">
         <v>2.4552</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5573</v>
+        <v>2.0185</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3562</v>
+        <v>-1.7974</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9136</v>
+        <v>3.816</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4396</v>
@@ -1702,13 +1702,13 @@
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0171</v>
+        <v>0.4783</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5804</v>
+        <v>-0.0216</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5975</v>
+        <v>0.4999</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2811</v>
+        <v>1.3929</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8817</v>
+        <v>1.9934</v>
       </c>
       <c r="F17" t="n">
         <v>-0.6006</v>
@@ -1780,10 +1780,10 @@
         <v>3.9151</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1935</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1082</v>
+        <v>0.2199</v>
       </c>
       <c r="U17" t="n">
         <v>-0.3016</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6562</v>
+        <v>-0.4943</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7197</v>
+        <v>-1.4962</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0635</v>
+        <v>1.0019</v>
       </c>
       <c r="G18" t="n">
         <v>-1.447</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0959</v>
+        <v>0.2578</v>
       </c>
       <c r="T18" t="n">
-        <v>0.024</v>
+        <v>0.2476</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8488</v>
+        <v>-0.5765</v>
       </c>
       <c r="E19" t="n">
         <v>0.5377</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3865</v>
+        <v>-1.1142</v>
       </c>
       <c r="G19" t="n">
         <v>2.8351</v>
@@ -1936,13 +1936,13 @@
         <v>2.6101</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3168</v>
+        <v>-0.0445</v>
       </c>
       <c r="T19" t="n">
         <v>0.0156</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3324</v>
+        <v>-0.0601</v>
       </c>
       <c r="V19" t="n">
         <v>-4.8897</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0622</v>
+        <v>-3.4997</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6016</v>
+        <v>-2.8251</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4606</v>
+        <v>-0.6745</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4066</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7209</v>
+        <v>-0.1583</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1214</v>
+        <v>-0.3449</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5995</v>
+        <v>0.1866</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3698</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3669</v>
+        <v>-5.1112</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8034</v>
+        <v>-1.6916</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5635</v>
+        <v>-3.4196</v>
       </c>
       <c r="G21" t="n">
         <v>-1.257</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6303</v>
+        <v>-0.3746</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3869</v>
+        <v>-0.2752</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2434</v>
+        <v>-0.0994</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3045</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.0909</v>
+        <v>-7.2566</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8943</v>
+        <v>-5.2296</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1966</v>
+        <v>-2.027</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9539</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3871</v>
+        <v>0.2214</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0277</v>
+        <v>-0.3076</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3594</v>
+        <v>0.529</v>
       </c>
       <c r="V22" t="n">
         <v>-2.609</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9674</v>
+        <v>-5.732200000000002</v>
       </c>
       <c r="E23" t="n">
         <v>-8.5596</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5924000000000005</v>
+        <v>2.8275</v>
       </c>
       <c r="G23" t="n">
         <v>-1.745</v>
@@ -2248,13 +2248,13 @@
         <v>20.6633</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3098</v>
+        <v>0.9254000000000002</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3063</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0034</v>
+        <v>1.2317</v>
       </c>
       <c r="V23" t="n">
         <v>-7.087500000000001</v>
